--- a/scripts/cities.xlsx
+++ b/scripts/cities.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="sheet7" sheetId="1" r:id="rId1"/>
+    <sheet name="sheet3" sheetId="1" r:id="rId1"/>
+    <sheet name="sheet4" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D169"/>
+  <dimension ref="A1:D219"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,2359 +416,3182 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>405</v>
+        <v>180</v>
       </c>
       <c r="B2" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C2" t="str">
-        <v>Bilaspur</v>
+        <v>Anantnag</v>
       </c>
       <c r="D2" t="str">
-        <v>Bilaspur</v>
+        <v>Anantnag</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>406</v>
+        <v>181</v>
       </c>
       <c r="B3" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C3" t="str">
-        <v>Bilaspur</v>
+        <v>Anantnag</v>
       </c>
       <c r="D3" t="str">
-        <v>Ghumarwin</v>
+        <v>Bijbehara</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>407</v>
+        <v>182</v>
       </c>
       <c r="B4" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C4" t="str">
-        <v>Bilaspur</v>
+        <v>Anantnag</v>
       </c>
       <c r="D4" t="str">
-        <v>Jhandutta</v>
+        <v>Dooru</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>408</v>
+        <v>183</v>
       </c>
       <c r="B5" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C5" t="str">
-        <v>Bilaspur</v>
+        <v>Anantnag</v>
       </c>
       <c r="D5" t="str">
-        <v>Naina Devi</v>
+        <v>Kokernag</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>409</v>
+        <v>184</v>
       </c>
       <c r="B6" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C6" t="str">
-        <v>Bilaspur</v>
+        <v>Anantnag</v>
       </c>
       <c r="D6" t="str">
-        <v>Swarghat</v>
+        <v>Pahalgam</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>410</v>
+        <v>185</v>
       </c>
       <c r="B7" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C7" t="str">
-        <v>Bilaspur</v>
+        <v>Anantnag</v>
       </c>
       <c r="D7" t="str">
-        <v>Talai</v>
+        <v>Srigufwara</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>411</v>
+        <v>186</v>
       </c>
       <c r="B8" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C8" t="str">
-        <v>Bilaspur</v>
+        <v>Anantnag</v>
       </c>
       <c r="D8" t="str">
-        <v>Berthin</v>
+        <v>Mattan</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>412</v>
+        <v>187</v>
       </c>
       <c r="B9" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C9" t="str">
-        <v>Bilaspur</v>
+        <v>Anantnag</v>
       </c>
       <c r="D9" t="str">
-        <v>Namhol</v>
+        <v>Achabal</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>413</v>
+        <v>188</v>
       </c>
       <c r="B10" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C10" t="str">
-        <v>Bilaspur</v>
+        <v>Anantnag</v>
       </c>
       <c r="D10" t="str">
-        <v>Bharari</v>
+        <v>Shangus</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>414</v>
+        <v>189</v>
       </c>
       <c r="B11" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C11" t="str">
-        <v>Bilaspur</v>
+        <v>Anantnag</v>
       </c>
       <c r="D11" t="str">
-        <v>Kot Kehloor</v>
+        <v>Aishmuqam</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>415</v>
+        <v>190</v>
       </c>
       <c r="B12" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C12" t="str">
-        <v>Bilaspur</v>
+        <v>Anantnag</v>
       </c>
       <c r="D12" t="str">
-        <v>Deoli</v>
+        <v>Verinag</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>416</v>
+        <v>191</v>
       </c>
       <c r="B13" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C13" t="str">
-        <v>Bilaspur</v>
+        <v>Anantnag</v>
       </c>
       <c r="D13" t="str">
-        <v>Kandrour</v>
+        <v>Hiller Shahabad</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>417</v>
+        <v>192</v>
       </c>
       <c r="B14" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C14" t="str">
-        <v>Bilaspur</v>
+        <v>Anantnag</v>
       </c>
       <c r="D14" t="str">
-        <v>Lehri Sarail</v>
+        <v>Breng</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>418</v>
+        <v>193</v>
       </c>
       <c r="B15" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C15" t="str">
-        <v>Chamba</v>
+        <v>Anantnag</v>
       </c>
       <c r="D15" t="str">
-        <v>Chamba</v>
+        <v>Larnoo</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>419</v>
+        <v>194</v>
       </c>
       <c r="B16" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C16" t="str">
-        <v>Chamba</v>
+        <v>Anantnag</v>
       </c>
       <c r="D16" t="str">
-        <v>Dalhousie</v>
+        <v>Dialgam</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>420</v>
+        <v>195</v>
       </c>
       <c r="B17" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C17" t="str">
-        <v>Chamba</v>
+        <v>Anantnag</v>
       </c>
       <c r="D17" t="str">
-        <v>Bharmour</v>
+        <v>Hakoora</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>421</v>
+        <v>196</v>
       </c>
       <c r="B18" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C18" t="str">
-        <v>Chamba</v>
+        <v>Anantnag</v>
       </c>
       <c r="D18" t="str">
-        <v>Banikhet</v>
+        <v>Vessu</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>422</v>
+        <v>197</v>
       </c>
       <c r="B19" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C19" t="str">
-        <v>Chamba</v>
+        <v>Anantnag</v>
       </c>
       <c r="D19" t="str">
-        <v>Tissa</v>
+        <v>Breng</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>423</v>
+        <v>198</v>
       </c>
       <c r="B20" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C20" t="str">
-        <v>Chamba</v>
+        <v>Anantnag</v>
       </c>
       <c r="D20" t="str">
-        <v>Salooni</v>
+        <v>Larnoo</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>424</v>
+        <v>199</v>
       </c>
       <c r="B21" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C21" t="str">
-        <v>Chamba</v>
+        <v>Anantnag</v>
       </c>
       <c r="D21" t="str">
-        <v>Mehla</v>
+        <v>Dialgam</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>425</v>
+        <v>200</v>
       </c>
       <c r="B22" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C22" t="str">
-        <v>Chamba</v>
+        <v>Anantnag</v>
       </c>
       <c r="D22" t="str">
-        <v>Holi</v>
+        <v>Hakoora</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>426</v>
+        <v>201</v>
       </c>
       <c r="B23" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C23" t="str">
-        <v>Chamba</v>
+        <v>Anantnag</v>
       </c>
       <c r="D23" t="str">
-        <v>Khajjiar</v>
+        <v>Vessu</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>427</v>
+        <v>202</v>
       </c>
       <c r="B24" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C24" t="str">
-        <v>Chamba</v>
+        <v>Bandipora</v>
       </c>
       <c r="D24" t="str">
-        <v>Saho</v>
+        <v>Bandipora</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>428</v>
+        <v>203</v>
       </c>
       <c r="B25" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C25" t="str">
-        <v>Chamba</v>
+        <v>Bandipora</v>
       </c>
       <c r="D25" t="str">
-        <v>Pangi</v>
+        <v>Hajin</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>429</v>
+        <v>204</v>
       </c>
       <c r="B26" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C26" t="str">
-        <v>Chamba</v>
+        <v>Bandipora</v>
       </c>
       <c r="D26" t="str">
-        <v>Sach</v>
+        <v>Sumbal</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>430</v>
+        <v>205</v>
       </c>
       <c r="B27" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C27" t="str">
-        <v>Chamba</v>
+        <v>Bandipora</v>
       </c>
       <c r="D27" t="str">
-        <v>Bairagarh</v>
+        <v>Ajas</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>431</v>
+        <v>206</v>
       </c>
       <c r="B28" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C28" t="str">
-        <v>Hamirpur</v>
+        <v>Bandipora</v>
       </c>
       <c r="D28" t="str">
-        <v>Hamirpur</v>
+        <v>Nadihal</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>432</v>
+        <v>207</v>
       </c>
       <c r="B29" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C29" t="str">
-        <v>Hamirpur</v>
+        <v>Bandipora</v>
       </c>
       <c r="D29" t="str">
-        <v>Nadaun</v>
+        <v>Aloosa</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>433</v>
+        <v>208</v>
       </c>
       <c r="B30" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C30" t="str">
-        <v>Hamirpur</v>
+        <v>Bandipora</v>
       </c>
       <c r="D30" t="str">
-        <v>Sujanpur Tira</v>
+        <v>Aragam</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>434</v>
+        <v>209</v>
       </c>
       <c r="B31" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C31" t="str">
-        <v>Hamirpur</v>
+        <v>Bandipora</v>
       </c>
       <c r="D31" t="str">
-        <v>Bhoranj</v>
+        <v>Quil Muqam</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>435</v>
+        <v>210</v>
       </c>
       <c r="B32" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C32" t="str">
-        <v>Hamirpur</v>
+        <v>Baramulla</v>
       </c>
       <c r="D32" t="str">
-        <v>Barsar</v>
+        <v>Baramulla</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>436</v>
+        <v>211</v>
       </c>
       <c r="B33" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C33" t="str">
-        <v>Hamirpur</v>
+        <v>Baramulla</v>
       </c>
       <c r="D33" t="str">
-        <v>Bhota</v>
+        <v>Sopore</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>437</v>
+        <v>212</v>
       </c>
       <c r="B34" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C34" t="str">
-        <v>Hamirpur</v>
+        <v>Baramulla</v>
       </c>
       <c r="D34" t="str">
-        <v>Tauni Devi</v>
+        <v>Uri</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>438</v>
+        <v>213</v>
       </c>
       <c r="B35" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C35" t="str">
-        <v>Hamirpur</v>
+        <v>Baramulla</v>
       </c>
       <c r="D35" t="str">
-        <v>Galore</v>
+        <v>Pattan</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>439</v>
+        <v>214</v>
       </c>
       <c r="B36" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C36" t="str">
-        <v>Hamirpur</v>
+        <v>Baramulla</v>
       </c>
       <c r="D36" t="str">
-        <v>Jol Sappar</v>
+        <v>Kreeri</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>440</v>
+        <v>215</v>
       </c>
       <c r="B37" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C37" t="str">
-        <v>Hamirpur</v>
+        <v>Baramulla</v>
       </c>
       <c r="D37" t="str">
-        <v>Lambloo</v>
+        <v>Tangmarg</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>441</v>
+        <v>216</v>
       </c>
       <c r="B38" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C38" t="str">
-        <v>Hamirpur</v>
+        <v>Baramulla</v>
       </c>
       <c r="D38" t="str">
-        <v>Dhaneta</v>
+        <v>Kunzer</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>442</v>
+        <v>217</v>
       </c>
       <c r="B39" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C39" t="str">
-        <v>Hamirpur</v>
+        <v>Baramulla</v>
       </c>
       <c r="D39" t="str">
-        <v>Jahu</v>
+        <v>Boniyar</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>443</v>
+        <v>218</v>
       </c>
       <c r="B40" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C40" t="str">
-        <v>Kangra</v>
+        <v>Baramulla</v>
       </c>
       <c r="D40" t="str">
-        <v>Dharamshala</v>
+        <v>Rohama</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>444</v>
+        <v>219</v>
       </c>
       <c r="B41" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C41" t="str">
-        <v>Kangra</v>
+        <v>Baramulla</v>
       </c>
       <c r="D41" t="str">
-        <v>Palampur</v>
+        <v>Wagoora</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>445</v>
+        <v>220</v>
       </c>
       <c r="B42" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C42" t="str">
-        <v>Kangra</v>
+        <v>Baramulla</v>
       </c>
       <c r="D42" t="str">
-        <v>Kangra</v>
+        <v>Watergam</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>446</v>
+        <v>221</v>
       </c>
       <c r="B43" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C43" t="str">
-        <v>Kangra</v>
+        <v>Baramulla</v>
       </c>
       <c r="D43" t="str">
-        <v>Baijnath</v>
+        <v>Delina</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>447</v>
+        <v>222</v>
       </c>
       <c r="B44" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C44" t="str">
-        <v>Kangra</v>
+        <v>Baramulla</v>
       </c>
       <c r="D44" t="str">
-        <v>Dehra Gopipur</v>
+        <v>Singhpora</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>448</v>
+        <v>223</v>
       </c>
       <c r="B45" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C45" t="str">
-        <v>Kangra</v>
+        <v>Baramulla</v>
       </c>
       <c r="D45" t="str">
-        <v>Nurpur</v>
+        <v>Chakloo</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>449</v>
+        <v>224</v>
       </c>
       <c r="B46" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C46" t="str">
-        <v>Kangra</v>
+        <v>Baramulla</v>
       </c>
       <c r="D46" t="str">
-        <v>Jawalamukhi</v>
+        <v>Sheeri</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>450</v>
+        <v>225</v>
       </c>
       <c r="B47" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C47" t="str">
-        <v>Kangra</v>
+        <v>Baramulla</v>
       </c>
       <c r="D47" t="str">
-        <v>Shahpur</v>
+        <v>Fatehgarh</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>451</v>
+        <v>226</v>
       </c>
       <c r="B48" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C48" t="str">
-        <v>Kangra</v>
+        <v>Budgam</v>
       </c>
       <c r="D48" t="str">
-        <v>Nagrota Bagwan</v>
+        <v>Budgam</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>452</v>
+        <v>227</v>
       </c>
       <c r="B49" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C49" t="str">
-        <v>Kangra</v>
+        <v>Budgam</v>
       </c>
       <c r="D49" t="str">
-        <v>Indora</v>
+        <v>Chadoora</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>453</v>
+        <v>228</v>
       </c>
       <c r="B50" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C50" t="str">
-        <v>Kangra</v>
+        <v>Budgam</v>
       </c>
       <c r="D50" t="str">
-        <v>Jassur</v>
+        <v>Beerwah</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>454</v>
+        <v>229</v>
       </c>
       <c r="B51" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C51" t="str">
-        <v>Kangra</v>
+        <v>Budgam</v>
       </c>
       <c r="D51" t="str">
-        <v>Yol</v>
+        <v>Khansahib</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>455</v>
+        <v>230</v>
       </c>
       <c r="B52" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C52" t="str">
-        <v>Kangra</v>
+        <v>Budgam</v>
       </c>
       <c r="D52" t="str">
-        <v>McLeod Ganj</v>
+        <v>Charar-e-Sharif</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>456</v>
+        <v>231</v>
       </c>
       <c r="B53" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C53" t="str">
-        <v>Kangra</v>
+        <v>Budgam</v>
       </c>
       <c r="D53" t="str">
-        <v>Sidhbari</v>
+        <v>Magam</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>457</v>
+        <v>232</v>
       </c>
       <c r="B54" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C54" t="str">
-        <v>Kangra</v>
+        <v>Budgam</v>
       </c>
       <c r="D54" t="str">
-        <v>Andretta</v>
+        <v>Narbal</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>458</v>
+        <v>233</v>
       </c>
       <c r="B55" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C55" t="str">
-        <v>Kangra</v>
+        <v>Budgam</v>
       </c>
       <c r="D55" t="str">
-        <v>Bir Billing</v>
+        <v>Pakherpora</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>459</v>
+        <v>234</v>
       </c>
       <c r="B56" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C56" t="str">
-        <v>Kangra</v>
+        <v>Budgam</v>
       </c>
       <c r="D56" t="str">
-        <v>Pragpur</v>
+        <v>Soibugh</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>460</v>
+        <v>235</v>
       </c>
       <c r="B57" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C57" t="str">
-        <v>Kangra</v>
+        <v>Budgam</v>
       </c>
       <c r="D57" t="str">
-        <v>Rakkar</v>
+        <v>Ichgam</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>461</v>
+        <v>236</v>
       </c>
       <c r="B58" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C58" t="str">
-        <v>Kangra</v>
+        <v>Budgam</v>
       </c>
       <c r="D58" t="str">
-        <v>Garli</v>
+        <v>Humhama</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>462</v>
+        <v>237</v>
       </c>
       <c r="B59" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C59" t="str">
-        <v>Kangra</v>
+        <v>Budgam</v>
       </c>
       <c r="D59" t="str">
-        <v>Khundian</v>
+        <v>Chattergam</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>463</v>
+        <v>238</v>
       </c>
       <c r="B60" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C60" t="str">
-        <v>Kangra</v>
+        <v>Budgam</v>
       </c>
       <c r="D60" t="str">
-        <v>Sansal</v>
+        <v>Khag</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>464</v>
+        <v>239</v>
       </c>
       <c r="B61" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C61" t="str">
-        <v>Kinnaur</v>
+        <v>Budgam</v>
       </c>
       <c r="D61" t="str">
-        <v>Reckong Peo</v>
+        <v>Daharmuna</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>465</v>
+        <v>240</v>
       </c>
       <c r="B62" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C62" t="str">
-        <v>Kinnaur</v>
+        <v>Doda</v>
       </c>
       <c r="D62" t="str">
-        <v>Kalpa</v>
+        <v>Doda</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>466</v>
+        <v>241</v>
       </c>
       <c r="B63" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C63" t="str">
-        <v>Kinnaur</v>
+        <v>Doda</v>
       </c>
       <c r="D63" t="str">
-        <v>Sangla</v>
+        <v>Bhaderwah</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>467</v>
+        <v>242</v>
       </c>
       <c r="B64" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C64" t="str">
-        <v>Kinnaur</v>
+        <v>Doda</v>
       </c>
       <c r="D64" t="str">
-        <v>Pooh</v>
+        <v>Thathri</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>468</v>
+        <v>243</v>
       </c>
       <c r="B65" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C65" t="str">
-        <v>Kinnaur</v>
+        <v>Doda</v>
       </c>
       <c r="D65" t="str">
-        <v>Nichar</v>
+        <v>Gandoh</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>469</v>
+        <v>244</v>
       </c>
       <c r="B66" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C66" t="str">
-        <v>Kinnaur</v>
+        <v>Doda</v>
       </c>
       <c r="D66" t="str">
-        <v>Ribba</v>
+        <v>Assar</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>470</v>
+        <v>245</v>
       </c>
       <c r="B67" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C67" t="str">
-        <v>Kinnaur</v>
+        <v>Doda</v>
       </c>
       <c r="D67" t="str">
-        <v>Moorang</v>
+        <v>Dessa</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>471</v>
+        <v>246</v>
       </c>
       <c r="B68" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C68" t="str">
-        <v>Kinnaur</v>
+        <v>Doda</v>
       </c>
       <c r="D68" t="str">
-        <v>Chitkul</v>
+        <v>Marmat</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>472</v>
+        <v>247</v>
       </c>
       <c r="B69" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C69" t="str">
-        <v>Kinnaur</v>
+        <v>Doda</v>
       </c>
       <c r="D69" t="str">
-        <v>Rakcham</v>
+        <v>Kahara</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>473</v>
+        <v>248</v>
       </c>
       <c r="B70" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C70" t="str">
-        <v>Kinnaur</v>
+        <v>Ganderbal</v>
       </c>
       <c r="D70" t="str">
-        <v>Ropa</v>
+        <v>Ganderbal</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>474</v>
+        <v>249</v>
       </c>
       <c r="B71" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C71" t="str">
-        <v>Kinnaur</v>
+        <v>Ganderbal</v>
       </c>
       <c r="D71" t="str">
-        <v>Akpa</v>
+        <v>Kangan</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>475</v>
+        <v>250</v>
       </c>
       <c r="B72" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C72" t="str">
-        <v>Kinnaur</v>
+        <v>Ganderbal</v>
       </c>
       <c r="D72" t="str">
-        <v>Pangi</v>
+        <v>Sonamarg</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>476</v>
+        <v>251</v>
       </c>
       <c r="B73" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C73" t="str">
-        <v>Kullu</v>
+        <v>Ganderbal</v>
       </c>
       <c r="D73" t="str">
-        <v>Kullu</v>
+        <v>Lar</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>477</v>
+        <v>252</v>
       </c>
       <c r="B74" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C74" t="str">
-        <v>Kullu</v>
+        <v>Ganderbal</v>
       </c>
       <c r="D74" t="str">
-        <v>Manali</v>
+        <v>Wakura</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>478</v>
+        <v>253</v>
       </c>
       <c r="B75" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C75" t="str">
-        <v>Kullu</v>
+        <v>Ganderbal</v>
       </c>
       <c r="D75" t="str">
-        <v>Banjar</v>
+        <v>Safapora</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>479</v>
+        <v>254</v>
       </c>
       <c r="B76" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C76" t="str">
-        <v>Kullu</v>
+        <v>Ganderbal</v>
       </c>
       <c r="D76" t="str">
-        <v>Bhuntar</v>
+        <v>Kullan</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>480</v>
+        <v>255</v>
       </c>
       <c r="B77" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C77" t="str">
-        <v>Kullu</v>
+        <v>Jammu</v>
       </c>
       <c r="D77" t="str">
-        <v>Naggar</v>
+        <v>Jammu</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>481</v>
+        <v>256</v>
       </c>
       <c r="B78" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C78" t="str">
-        <v>Kullu</v>
+        <v>Jammu</v>
       </c>
       <c r="D78" t="str">
-        <v>Ani</v>
+        <v>Akhnoor</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>482</v>
+        <v>257</v>
       </c>
       <c r="B79" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C79" t="str">
-        <v>Kullu</v>
+        <v>Jammu</v>
       </c>
       <c r="D79" t="str">
-        <v>Sainj</v>
+        <v>Bishnah</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>483</v>
+        <v>258</v>
       </c>
       <c r="B80" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C80" t="str">
-        <v>Kullu</v>
+        <v>Jammu</v>
       </c>
       <c r="D80" t="str">
-        <v>Bajaura</v>
+        <v>R.S. Pura</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>484</v>
+        <v>259</v>
       </c>
       <c r="B81" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C81" t="str">
-        <v>Kullu</v>
+        <v>Jammu</v>
       </c>
       <c r="D81" t="str">
-        <v>Kasol</v>
+        <v>Marh</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>485</v>
+        <v>260</v>
       </c>
       <c r="B82" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C82" t="str">
-        <v>Kullu</v>
+        <v>Jammu</v>
       </c>
       <c r="D82" t="str">
-        <v>Tosh</v>
+        <v>Jourian</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>486</v>
+        <v>261</v>
       </c>
       <c r="B83" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C83" t="str">
-        <v>Kullu</v>
+        <v>Jammu</v>
       </c>
       <c r="D83" t="str">
-        <v>Malana</v>
+        <v>Khour</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>487</v>
+        <v>262</v>
       </c>
       <c r="B84" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C84" t="str">
-        <v>Kullu</v>
+        <v>Jammu</v>
       </c>
       <c r="D84" t="str">
-        <v>Jibhi</v>
+        <v>Satwari</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>488</v>
+        <v>263</v>
       </c>
       <c r="B85" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C85" t="str">
-        <v>Kullu</v>
+        <v>Jammu</v>
       </c>
       <c r="D85" t="str">
-        <v>Shoja</v>
+        <v>Domana</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>489</v>
+        <v>264</v>
       </c>
       <c r="B86" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C86" t="str">
-        <v>Kullu</v>
+        <v>Jammu</v>
       </c>
       <c r="D86" t="str">
-        <v>Katrain</v>
+        <v>Bhalwal</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>490</v>
+        <v>265</v>
       </c>
       <c r="B87" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C87" t="str">
-        <v>Lahaul and Spiti</v>
+        <v>Jammu</v>
       </c>
       <c r="D87" t="str">
-        <v>Keylong</v>
+        <v>Arnia</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>491</v>
+        <v>266</v>
       </c>
       <c r="B88" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C88" t="str">
-        <v>Lahaul and Spiti</v>
+        <v>Jammu</v>
       </c>
       <c r="D88" t="str">
-        <v>Kaza</v>
+        <v>Miran Sahib</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>492</v>
+        <v>267</v>
       </c>
       <c r="B89" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C89" t="str">
-        <v>Lahaul and Spiti</v>
+        <v>Jammu</v>
       </c>
       <c r="D89" t="str">
-        <v>Udaipur</v>
+        <v>Gharota</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>493</v>
+        <v>268</v>
       </c>
       <c r="B90" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C90" t="str">
-        <v>Lahaul and Spiti</v>
+        <v>Jammu</v>
       </c>
       <c r="D90" t="str">
-        <v>Tabo</v>
+        <v>Raipur Domana</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>494</v>
+        <v>269</v>
       </c>
       <c r="B91" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C91" t="str">
-        <v>Lahaul and Spiti</v>
+        <v>Jammu</v>
       </c>
       <c r="D91" t="str">
-        <v>Losar</v>
+        <v>Chakroi</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>495</v>
+        <v>270</v>
       </c>
       <c r="B92" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C92" t="str">
-        <v>Lahaul and Spiti</v>
+        <v>Jammu</v>
       </c>
       <c r="D92" t="str">
-        <v>Sissu</v>
+        <v>Suchetgarh</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>496</v>
+        <v>271</v>
       </c>
       <c r="B93" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C93" t="str">
-        <v>Lahaul and Spiti</v>
+        <v>Jammu</v>
       </c>
       <c r="D93" t="str">
-        <v>Gondhla</v>
+        <v>Pragwal</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>497</v>
+        <v>272</v>
       </c>
       <c r="B94" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C94" t="str">
-        <v>Lahaul and Spiti</v>
+        <v>Kathua</v>
       </c>
       <c r="D94" t="str">
-        <v>Dhankar</v>
+        <v>Kathua</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>498</v>
+        <v>273</v>
       </c>
       <c r="B95" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C95" t="str">
-        <v>Lahaul and Spiti</v>
+        <v>Kathua</v>
       </c>
       <c r="D95" t="str">
-        <v>Kibber</v>
+        <v>Hiranagar</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>499</v>
+        <v>274</v>
       </c>
       <c r="B96" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C96" t="str">
-        <v>Lahaul and Spiti</v>
+        <v>Kathua</v>
       </c>
       <c r="D96" t="str">
-        <v>Komic</v>
+        <v>Billawar</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>500</v>
+        <v>275</v>
       </c>
       <c r="B97" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C97" t="str">
-        <v>Lahaul and Spiti</v>
+        <v>Kathua</v>
       </c>
       <c r="D97" t="str">
-        <v>Hikkim</v>
+        <v>Basohli</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>501</v>
+        <v>276</v>
       </c>
       <c r="B98" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C98" t="str">
-        <v>Lahaul and Spiti</v>
+        <v>Kathua</v>
       </c>
       <c r="D98" t="str">
-        <v>Langza</v>
+        <v>Lakhanpur</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>502</v>
+        <v>277</v>
       </c>
       <c r="B99" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C99" t="str">
-        <v>Mandi</v>
+        <v>Kathua</v>
       </c>
       <c r="D99" t="str">
-        <v>Mandi</v>
+        <v>Nagri</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>503</v>
+        <v>278</v>
       </c>
       <c r="B100" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C100" t="str">
-        <v>Mandi</v>
+        <v>Kathua</v>
       </c>
       <c r="D100" t="str">
-        <v>Sundernagar</v>
+        <v>Dayalachak</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>504</v>
+        <v>279</v>
       </c>
       <c r="B101" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C101" t="str">
-        <v>Mandi</v>
+        <v>Kathua</v>
       </c>
       <c r="D101" t="str">
-        <v>Jogindernagar</v>
+        <v>Mahanpur</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>505</v>
+        <v>280</v>
       </c>
       <c r="B102" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C102" t="str">
-        <v>Mandi</v>
+        <v>Kathua</v>
       </c>
       <c r="D102" t="str">
-        <v>Karsog</v>
+        <v>Bani</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>506</v>
+        <v>281</v>
       </c>
       <c r="B103" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C103" t="str">
-        <v>Mandi</v>
+        <v>Kathua</v>
       </c>
       <c r="D103" t="str">
-        <v>Sarkaghat</v>
+        <v>Chadwal</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>507</v>
+        <v>282</v>
       </c>
       <c r="B104" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C104" t="str">
-        <v>Mandi</v>
+        <v>Kathua</v>
       </c>
       <c r="D104" t="str">
-        <v>Padhar</v>
+        <v>Marheen</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>508</v>
+        <v>283</v>
       </c>
       <c r="B105" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C105" t="str">
-        <v>Mandi</v>
+        <v>Kathua</v>
       </c>
       <c r="D105" t="str">
-        <v>Ner Chowk</v>
+        <v>Parole</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>509</v>
+        <v>284</v>
       </c>
       <c r="B106" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C106" t="str">
-        <v>Mandi</v>
+        <v>Kathua</v>
       </c>
       <c r="D106" t="str">
-        <v>Rewalsar</v>
+        <v>Hatli</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>510</v>
+        <v>285</v>
       </c>
       <c r="B107" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C107" t="str">
-        <v>Mandi</v>
+        <v>Kathua</v>
       </c>
       <c r="D107" t="str">
-        <v>Gohar</v>
+        <v>Kore Punnu</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>511</v>
+        <v>286</v>
       </c>
       <c r="B108" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C108" t="str">
-        <v>Mandi</v>
+        <v>Kishtwar</v>
       </c>
       <c r="D108" t="str">
-        <v>Kotli</v>
+        <v>Kishtwar</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>512</v>
+        <v>287</v>
       </c>
       <c r="B109" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C109" t="str">
-        <v>Mandi</v>
+        <v>Kishtwar</v>
       </c>
       <c r="D109" t="str">
-        <v>Barot</v>
+        <v>Chhatroo</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>513</v>
+        <v>288</v>
       </c>
       <c r="B110" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C110" t="str">
-        <v>Mandi</v>
+        <v>Kishtwar</v>
       </c>
       <c r="D110" t="str">
-        <v>Janjheli</v>
+        <v>Drabshalla</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>514</v>
+        <v>289</v>
       </c>
       <c r="B111" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C111" t="str">
-        <v>Mandi</v>
+        <v>Kishtwar</v>
       </c>
       <c r="D111" t="str">
-        <v>Thunag</v>
+        <v>Paddar</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>515</v>
+        <v>290</v>
       </c>
       <c r="B112" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C112" t="str">
-        <v>Mandi</v>
+        <v>Kishtwar</v>
       </c>
       <c r="D112" t="str">
-        <v>Bagsiad</v>
+        <v>Marwah</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>516</v>
+        <v>291</v>
       </c>
       <c r="B113" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C113" t="str">
-        <v>Mandi</v>
+        <v>Kishtwar</v>
       </c>
       <c r="D113" t="str">
-        <v>Chail Chowk</v>
+        <v>Dachhan</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>517</v>
+        <v>292</v>
       </c>
       <c r="B114" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C114" t="str">
-        <v>Shimla</v>
+        <v>Kishtwar</v>
       </c>
       <c r="D114" t="str">
-        <v>Shimla</v>
+        <v>Atholi</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>518</v>
+        <v>293</v>
       </c>
       <c r="B115" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C115" t="str">
-        <v>Shimla</v>
+        <v>Kulgam</v>
       </c>
       <c r="D115" t="str">
-        <v>Theog</v>
+        <v>Kulgam</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>519</v>
+        <v>294</v>
       </c>
       <c r="B116" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C116" t="str">
-        <v>Shimla</v>
+        <v>Kulgam</v>
       </c>
       <c r="D116" t="str">
-        <v>Rohru</v>
+        <v>Qazigund</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>520</v>
+        <v>295</v>
       </c>
       <c r="B117" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C117" t="str">
-        <v>Shimla</v>
+        <v>Kulgam</v>
       </c>
       <c r="D117" t="str">
-        <v>Rampur Bushahr</v>
+        <v>Devsar</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>521</v>
+        <v>296</v>
       </c>
       <c r="B118" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C118" t="str">
-        <v>Shimla</v>
+        <v>Kulgam</v>
       </c>
       <c r="D118" t="str">
-        <v>Narkanda</v>
+        <v>Yaripora</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>522</v>
+        <v>297</v>
       </c>
       <c r="B119" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C119" t="str">
-        <v>Shimla</v>
+        <v>Kulgam</v>
       </c>
       <c r="D119" t="str">
-        <v>Chopal</v>
+        <v>Frisal</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>523</v>
+        <v>298</v>
       </c>
       <c r="B120" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C120" t="str">
-        <v>Shimla</v>
+        <v>Kulgam</v>
       </c>
       <c r="D120" t="str">
-        <v>Kotkhai</v>
+        <v>D.H. Pora</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>524</v>
+        <v>299</v>
       </c>
       <c r="B121" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C121" t="str">
-        <v>Shimla</v>
+        <v>Kulgam</v>
       </c>
       <c r="D121" t="str">
-        <v>Jubbal</v>
+        <v>Kund</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>525</v>
+        <v>300</v>
       </c>
       <c r="B122" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C122" t="str">
-        <v>Shimla</v>
+        <v>Kupwara</v>
       </c>
       <c r="D122" t="str">
-        <v>Kufri</v>
+        <v>Kupwara</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>526</v>
+        <v>301</v>
       </c>
       <c r="B123" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C123" t="str">
-        <v>Shimla</v>
+        <v>Kupwara</v>
       </c>
       <c r="D123" t="str">
-        <v>Mashobra</v>
+        <v>Handwara</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>527</v>
+        <v>302</v>
       </c>
       <c r="B124" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C124" t="str">
-        <v>Shimla</v>
+        <v>Kupwara</v>
       </c>
       <c r="D124" t="str">
-        <v>Sunni</v>
+        <v>Langate</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>528</v>
+        <v>303</v>
       </c>
       <c r="B125" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C125" t="str">
-        <v>Shimla</v>
+        <v>Kupwara</v>
       </c>
       <c r="D125" t="str">
-        <v>Kumarsain</v>
+        <v>Kralpora</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>529</v>
+        <v>304</v>
       </c>
       <c r="B126" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C126" t="str">
-        <v>Shimla</v>
+        <v>Kupwara</v>
       </c>
       <c r="D126" t="str">
-        <v>Fagu</v>
+        <v>Karnah</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>530</v>
+        <v>305</v>
       </c>
       <c r="B127" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C127" t="str">
-        <v>Shimla</v>
+        <v>Kupwara</v>
       </c>
       <c r="D127" t="str">
-        <v>Tattapani</v>
+        <v>Trehgam</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>531</v>
+        <v>306</v>
       </c>
       <c r="B128" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C128" t="str">
-        <v>Shimla</v>
+        <v>Kupwara</v>
       </c>
       <c r="D128" t="str">
-        <v>Naldehra</v>
+        <v>Lalpora</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>532</v>
+        <v>307</v>
       </c>
       <c r="B129" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C129" t="str">
-        <v>Shimla</v>
+        <v>Kupwara</v>
       </c>
       <c r="D129" t="str">
-        <v>Junga</v>
+        <v>Sogam</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>533</v>
+        <v>308</v>
       </c>
       <c r="B130" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C130" t="str">
-        <v>Shimla</v>
+        <v>Kupwara</v>
       </c>
       <c r="D130" t="str">
-        <v>Chirgaon</v>
+        <v>Zachaldara</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>534</v>
+        <v>309</v>
       </c>
       <c r="B131" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C131" t="str">
-        <v>Sirmaur</v>
+        <v>Kupwara</v>
       </c>
       <c r="D131" t="str">
-        <v>Nahan</v>
+        <v>Keran</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>535</v>
+        <v>310</v>
       </c>
       <c r="B132" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C132" t="str">
-        <v>Sirmaur</v>
+        <v>Kupwara</v>
       </c>
       <c r="D132" t="str">
-        <v>Paonta Sahib</v>
+        <v>Machil</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>536</v>
+        <v>311</v>
       </c>
       <c r="B133" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C133" t="str">
-        <v>Sirmaur</v>
+        <v>Kupwara</v>
       </c>
       <c r="D133" t="str">
-        <v>Rajgarh</v>
+        <v>Teetwal</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>537</v>
+        <v>312</v>
       </c>
       <c r="B134" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C134" t="str">
-        <v>Sirmaur</v>
+        <v>Kupwara</v>
       </c>
       <c r="D134" t="str">
-        <v>Shillai</v>
+        <v>Chowkibal</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>538</v>
+        <v>313</v>
       </c>
       <c r="B135" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C135" t="str">
-        <v>Sirmaur</v>
+        <v>Kupwara</v>
       </c>
       <c r="D135" t="str">
-        <v>Sangrah</v>
+        <v>Kandi</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>539</v>
+        <v>314</v>
       </c>
       <c r="B136" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C136" t="str">
-        <v>Sirmaur</v>
+        <v>Poonch</v>
       </c>
       <c r="D136" t="str">
-        <v>Dadahu</v>
+        <v>Poonch</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>540</v>
+        <v>315</v>
       </c>
       <c r="B137" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C137" t="str">
-        <v>Sirmaur</v>
+        <v>Poonch</v>
       </c>
       <c r="D137" t="str">
-        <v>Sarahan</v>
+        <v>Mendhar</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>541</v>
+        <v>316</v>
       </c>
       <c r="B138" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C138" t="str">
-        <v>Sirmaur</v>
+        <v>Poonch</v>
       </c>
       <c r="D138" t="str">
-        <v>Kala Amb</v>
+        <v>Surankote</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>542</v>
+        <v>317</v>
       </c>
       <c r="B139" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C139" t="str">
-        <v>Sirmaur</v>
+        <v>Poonch</v>
       </c>
       <c r="D139" t="str">
-        <v>Renuka</v>
+        <v>Mandi</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>543</v>
+        <v>318</v>
       </c>
       <c r="B140" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C140" t="str">
-        <v>Sirmaur</v>
+        <v>Poonch</v>
       </c>
       <c r="D140" t="str">
-        <v>Haripurdhar</v>
+        <v>Balakote</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>544</v>
+        <v>319</v>
       </c>
       <c r="B141" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C141" t="str">
-        <v>Sirmaur</v>
+        <v>Poonch</v>
       </c>
       <c r="D141" t="str">
-        <v>Jamta</v>
+        <v>Bufliaz</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>545</v>
+        <v>320</v>
       </c>
       <c r="B142" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C142" t="str">
-        <v>Sirmaur</v>
+        <v>Poonch</v>
       </c>
       <c r="D142" t="str">
-        <v>Puruwala</v>
+        <v>Sathra</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>546</v>
+        <v>321</v>
       </c>
       <c r="B143" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C143" t="str">
-        <v>Sirmaur</v>
+        <v>Pulwama</v>
       </c>
       <c r="D143" t="str">
-        <v>Nohradhar</v>
+        <v>Pulwama</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>547</v>
+        <v>322</v>
       </c>
       <c r="B144" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C144" t="str">
-        <v>Solan</v>
+        <v>Pulwama</v>
       </c>
       <c r="D144" t="str">
-        <v>Solan</v>
+        <v>Pampore</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>548</v>
+        <v>323</v>
       </c>
       <c r="B145" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C145" t="str">
-        <v>Solan</v>
+        <v>Pulwama</v>
       </c>
       <c r="D145" t="str">
-        <v>Baddi</v>
+        <v>Tral</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>549</v>
+        <v>324</v>
       </c>
       <c r="B146" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C146" t="str">
-        <v>Solan</v>
+        <v>Pulwama</v>
       </c>
       <c r="D146" t="str">
-        <v>Nalagarh</v>
+        <v>Awantipora</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>550</v>
+        <v>325</v>
       </c>
       <c r="B147" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C147" t="str">
-        <v>Solan</v>
+        <v>Pulwama</v>
       </c>
       <c r="D147" t="str">
-        <v>Parwanoo</v>
+        <v>Rajpora</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>551</v>
+        <v>326</v>
       </c>
       <c r="B148" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C148" t="str">
-        <v>Solan</v>
+        <v>Pulwama</v>
       </c>
       <c r="D148" t="str">
-        <v>Kasauli</v>
+        <v>Kakapora</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>552</v>
+        <v>327</v>
       </c>
       <c r="B149" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C149" t="str">
-        <v>Solan</v>
+        <v>Pulwama</v>
       </c>
       <c r="D149" t="str">
-        <v>Arki</v>
+        <v>Litter</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>553</v>
+        <v>328</v>
       </c>
       <c r="B150" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C150" t="str">
-        <v>Solan</v>
+        <v>Pulwama</v>
       </c>
       <c r="D150" t="str">
-        <v>Barotiwala</v>
+        <v>Newa</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>554</v>
+        <v>329</v>
       </c>
       <c r="B151" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C151" t="str">
-        <v>Solan</v>
+        <v>Pulwama</v>
       </c>
       <c r="D151" t="str">
-        <v>Dharampur</v>
+        <v>Tahab</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>555</v>
+        <v>330</v>
       </c>
       <c r="B152" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C152" t="str">
-        <v>Solan</v>
+        <v>Pulwama</v>
       </c>
       <c r="D152" t="str">
-        <v>Subathu</v>
+        <v>Ratnipora</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>556</v>
+        <v>331</v>
       </c>
       <c r="B153" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C153" t="str">
-        <v>Solan</v>
+        <v>Pulwama</v>
       </c>
       <c r="D153" t="str">
-        <v>Chail</v>
+        <v>Aripal</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>557</v>
+        <v>332</v>
       </c>
       <c r="B154" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C154" t="str">
-        <v>Solan</v>
+        <v>Pulwama</v>
       </c>
       <c r="D154" t="str">
-        <v>Kunihar</v>
+        <v>Pinglena</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>558</v>
+        <v>333</v>
       </c>
       <c r="B155" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C155" t="str">
-        <v>Solan</v>
+        <v>Pulwama</v>
       </c>
       <c r="D155" t="str">
-        <v>Saproon</v>
+        <v>Karimabad</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>559</v>
+        <v>334</v>
       </c>
       <c r="B156" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C156" t="str">
-        <v>Solan</v>
+        <v>Rajouri</v>
       </c>
       <c r="D156" t="str">
-        <v>Waknaghat</v>
+        <v>Rajouri</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>560</v>
+        <v>335</v>
       </c>
       <c r="B157" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C157" t="str">
-        <v>Solan</v>
+        <v>Rajouri</v>
       </c>
       <c r="D157" t="str">
-        <v>Kumarhatti</v>
+        <v>Nowshera</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>561</v>
+        <v>336</v>
       </c>
       <c r="B158" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C158" t="str">
-        <v>Una</v>
+        <v>Rajouri</v>
       </c>
       <c r="D158" t="str">
-        <v>Una</v>
+        <v>Sunderbani</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>562</v>
+        <v>337</v>
       </c>
       <c r="B159" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C159" t="str">
-        <v>Una</v>
+        <v>Rajouri</v>
       </c>
       <c r="D159" t="str">
-        <v>Amb</v>
+        <v>Thanamandi</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>563</v>
+        <v>338</v>
       </c>
       <c r="B160" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C160" t="str">
-        <v>Una</v>
+        <v>Rajouri</v>
       </c>
       <c r="D160" t="str">
-        <v>Haroli</v>
+        <v>Darhal</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>564</v>
+        <v>339</v>
       </c>
       <c r="B161" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C161" t="str">
-        <v>Una</v>
+        <v>Rajouri</v>
       </c>
       <c r="D161" t="str">
-        <v>Gagret</v>
+        <v>Kalakote</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>565</v>
+        <v>340</v>
       </c>
       <c r="B162" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C162" t="str">
-        <v>Una</v>
+        <v>Rajouri</v>
       </c>
       <c r="D162" t="str">
-        <v>Bangana</v>
+        <v>Budhal</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>566</v>
+        <v>341</v>
       </c>
       <c r="B163" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C163" t="str">
-        <v>Una</v>
+        <v>Rajouri</v>
       </c>
       <c r="D163" t="str">
-        <v>Mehatpur</v>
+        <v>Manjakote</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>567</v>
+        <v>342</v>
       </c>
       <c r="B164" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C164" t="str">
-        <v>Una</v>
+        <v>Rajouri</v>
       </c>
       <c r="D164" t="str">
-        <v>Daulatpur Chowk</v>
+        <v>Doongi</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>568</v>
+        <v>343</v>
       </c>
       <c r="B165" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C165" t="str">
-        <v>Una</v>
+        <v>Rajouri</v>
       </c>
       <c r="D165" t="str">
-        <v>Basal</v>
+        <v>Lam</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>569</v>
+        <v>344</v>
       </c>
       <c r="B166" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C166" t="str">
-        <v>Una</v>
+        <v>Rajouri</v>
       </c>
       <c r="D166" t="str">
-        <v>Mubarikpur</v>
+        <v>Seri</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>570</v>
+        <v>345</v>
       </c>
       <c r="B167" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C167" t="str">
-        <v>Una</v>
+        <v>Rajouri</v>
       </c>
       <c r="D167" t="str">
-        <v>Tahliwal</v>
+        <v>Dhangri</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>571</v>
+        <v>346</v>
       </c>
       <c r="B168" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C168" t="str">
-        <v>Una</v>
+        <v>Rajouri</v>
       </c>
       <c r="D168" t="str">
-        <v>Santokhgarh</v>
+        <v>Chingus</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>572</v>
+        <v>347</v>
       </c>
       <c r="B169" t="str">
-        <v>Himachal Pradesh</v>
+        <v>Jammu &amp; Kashmir</v>
       </c>
       <c r="C169" t="str">
-        <v>Una</v>
+        <v>Ramban</v>
       </c>
       <c r="D169" t="str">
-        <v>Raipur Maidan</v>
+        <v>Ramban</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>348</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C170" t="str">
+        <v>Ramban</v>
+      </c>
+      <c r="D170" t="str">
+        <v>Banihal</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>349</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C171" t="str">
+        <v>Ramban</v>
+      </c>
+      <c r="D171" t="str">
+        <v>Gool</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>350</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C172" t="str">
+        <v>Ramban</v>
+      </c>
+      <c r="D172" t="str">
+        <v>Batote</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>351</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C173" t="str">
+        <v>Ramban</v>
+      </c>
+      <c r="D173" t="str">
+        <v>Ramsoo</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>352</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C174" t="str">
+        <v>Ramban</v>
+      </c>
+      <c r="D174" t="str">
+        <v>Rajgarh</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>353</v>
+      </c>
+      <c r="B175" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C175" t="str">
+        <v>Ramban</v>
+      </c>
+      <c r="D175" t="str">
+        <v>Sangaldan</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>354</v>
+      </c>
+      <c r="B176" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C176" t="str">
+        <v>Reasi</v>
+      </c>
+      <c r="D176" t="str">
+        <v>Reasi</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>355</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C177" t="str">
+        <v>Reasi</v>
+      </c>
+      <c r="D177" t="str">
+        <v>Katra</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>356</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C178" t="str">
+        <v>Reasi</v>
+      </c>
+      <c r="D178" t="str">
+        <v>Pouni</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>357</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C179" t="str">
+        <v>Reasi</v>
+      </c>
+      <c r="D179" t="str">
+        <v>Arnas</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>358</v>
+      </c>
+      <c r="B180" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C180" t="str">
+        <v>Reasi</v>
+      </c>
+      <c r="D180" t="str">
+        <v>Mahore</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>359</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C181" t="str">
+        <v>Reasi</v>
+      </c>
+      <c r="D181" t="str">
+        <v>Jyotipuram</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>360</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C182" t="str">
+        <v>Reasi</v>
+      </c>
+      <c r="D182" t="str">
+        <v>Talwara</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>361</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C183" t="str">
+        <v>Reasi</v>
+      </c>
+      <c r="D183" t="str">
+        <v>Salal</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>362</v>
+      </c>
+      <c r="B184" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C184" t="str">
+        <v>Reasi</v>
+      </c>
+      <c r="D184" t="str">
+        <v>Bhomag</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>363</v>
+      </c>
+      <c r="B185" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C185" t="str">
+        <v>Reasi</v>
+      </c>
+      <c r="D185" t="str">
+        <v>Chassana</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>364</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C186" t="str">
+        <v>Reasi</v>
+      </c>
+      <c r="D186" t="str">
+        <v>Kansi Patta</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>365</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C187" t="str">
+        <v>Reasi</v>
+      </c>
+      <c r="D187" t="str">
+        <v>Tuli</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>366</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C188" t="str">
+        <v>Samba</v>
+      </c>
+      <c r="D188" t="str">
+        <v>Samba</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>367</v>
+      </c>
+      <c r="B189" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C189" t="str">
+        <v>Samba</v>
+      </c>
+      <c r="D189" t="str">
+        <v>Vijaypur</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>368</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C190" t="str">
+        <v>Samba</v>
+      </c>
+      <c r="D190" t="str">
+        <v>Bari Brahmana</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>369</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C191" t="str">
+        <v>Samba</v>
+      </c>
+      <c r="D191" t="str">
+        <v>Ghagwal</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>370</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C192" t="str">
+        <v>Samba</v>
+      </c>
+      <c r="D192" t="str">
+        <v>Ramgarh</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>371</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C193" t="str">
+        <v>Samba</v>
+      </c>
+      <c r="D193" t="str">
+        <v>Nud</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>372</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C194" t="str">
+        <v>Samba</v>
+      </c>
+      <c r="D194" t="str">
+        <v>Purmandal</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>373</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C195" t="str">
+        <v>Samba</v>
+      </c>
+      <c r="D195" t="str">
+        <v>Supwal</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>374</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C196" t="str">
+        <v>Samba</v>
+      </c>
+      <c r="D196" t="str">
+        <v>Rajpura</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>375</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C197" t="str">
+        <v>Samba</v>
+      </c>
+      <c r="D197" t="str">
+        <v>Sumb</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>376</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C198" t="str">
+        <v>Samba</v>
+      </c>
+      <c r="D198" t="str">
+        <v>Rakh Amb Talli</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>377</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C199" t="str">
+        <v>Samba</v>
+      </c>
+      <c r="D199" t="str">
+        <v>Patli</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>378</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C200" t="str">
+        <v>Shopian</v>
+      </c>
+      <c r="D200" t="str">
+        <v>Shopian</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>379</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C201" t="str">
+        <v>Shopian</v>
+      </c>
+      <c r="D201" t="str">
+        <v>Zainapora</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>380</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C202" t="str">
+        <v>Shopian</v>
+      </c>
+      <c r="D202" t="str">
+        <v>Keller</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>381</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C203" t="str">
+        <v>Shopian</v>
+      </c>
+      <c r="D203" t="str">
+        <v>Imamsahib</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>382</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C204" t="str">
+        <v>Shopian</v>
+      </c>
+      <c r="D204" t="str">
+        <v>Hirpora</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>383</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C205" t="str">
+        <v>Shopian</v>
+      </c>
+      <c r="D205" t="str">
+        <v>Vehil</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>384</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C206" t="str">
+        <v>Srinagar</v>
+      </c>
+      <c r="D206" t="str">
+        <v>Srinagar</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>385</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C207" t="str">
+        <v>Srinagar</v>
+      </c>
+      <c r="D207" t="str">
+        <v>Hazratbal</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>386</v>
+      </c>
+      <c r="B208" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C208" t="str">
+        <v>Srinagar</v>
+      </c>
+      <c r="D208" t="str">
+        <v>Zadibal</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>387</v>
+      </c>
+      <c r="B209" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C209" t="str">
+        <v>Srinagar</v>
+      </c>
+      <c r="D209" t="str">
+        <v>Chanapora</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>388</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C210" t="str">
+        <v>Srinagar</v>
+      </c>
+      <c r="D210" t="str">
+        <v>Eidgah</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>389</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Srinagar</v>
+      </c>
+      <c r="D211" t="str">
+        <v>Nishat</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>390</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Srinagar</v>
+      </c>
+      <c r="D212" t="str">
+        <v>Nowhatta</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>391</v>
+      </c>
+      <c r="B213" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C213" t="str">
+        <v>Srinagar</v>
+      </c>
+      <c r="D213" t="str">
+        <v>Panthachowk</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>392</v>
+      </c>
+      <c r="B214" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C214" t="str">
+        <v>Srinagar</v>
+      </c>
+      <c r="D214" t="str">
+        <v>Shalimar</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>393</v>
+      </c>
+      <c r="B215" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C215" t="str">
+        <v>Udhampur</v>
+      </c>
+      <c r="D215" t="str">
+        <v>Udhampur</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>394</v>
+      </c>
+      <c r="B216" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C216" t="str">
+        <v>Udhampur</v>
+      </c>
+      <c r="D216" t="str">
+        <v>Chenani</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>395</v>
+      </c>
+      <c r="B217" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C217" t="str">
+        <v>Udhampur</v>
+      </c>
+      <c r="D217" t="str">
+        <v>Ramnagar</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>396</v>
+      </c>
+      <c r="B218" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C218" t="str">
+        <v>Udhampur</v>
+      </c>
+      <c r="D218" t="str">
+        <v>Panchari</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>397</v>
+      </c>
+      <c r="B219" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C219" t="str">
+        <v>Udhampur</v>
+      </c>
+      <c r="D219" t="str">
+        <v>Majalta</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D169"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D219"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D8"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Sr No</v>
+      </c>
+      <c r="B1" t="str">
+        <v>State</v>
+      </c>
+      <c r="C1" t="str">
+        <v>District</v>
+      </c>
+      <c r="D1" t="str">
+        <v>City / Town / Urban Area</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>398</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Udhampur</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Tikri</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>399</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Udhampur</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Basantgarh</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>400</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Udhampur</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Latti</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>401</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Udhampur</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Mongri</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>402</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Udhampur</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Dudu</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>403</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Udhampur</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Ghordi</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>404</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Jammu &amp; Kashmir</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Udhampur</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Jib</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D8"/>
   </ignoredErrors>
 </worksheet>
 </file>